--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_219_R22.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_219_R22.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1212</v>
+        <v>1.1308</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1199</v>
+        <v>3.5917</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.9987</v>
+        <v>-2.461</v>
       </c>
       <c r="G2" t="n">
         <v>3.7206</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.7078</v>
+        <v>-1.6983</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4936</v>
+        <v>-1.0218</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2142</v>
+        <v>-0.6765</v>
       </c>
       <c r="V2" t="n">
         <v>1.8919</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2571</v>
+        <v>-1.065</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3338</v>
+        <v>-0.138</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5909</v>
+        <v>-0.927</v>
       </c>
       <c r="G3" t="n">
         <v>-1.4658</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.224</v>
+        <v>-0.5838</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2592</v>
+        <v>-0.731</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4832</v>
+        <v>0.1472</v>
       </c>
       <c r="V3" t="n">
         <v>2.1444</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>A. LAKIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.7243</v>
+        <v>-2.8041</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2725</v>
+        <v>-1.4082</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.4518</v>
+        <v>-1.3959</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.0614</v>
+        <v>-2.92</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1475</v>
+        <v>-1.6386</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.9139</v>
+        <v>-1.2814</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2983</v>
+        <v>-0.8973</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1043</v>
+        <v>-0.9341</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1939</v>
+        <v>0.0368</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.3596</v>
+        <v>-2.0227</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2518</v>
+        <v>-0.7045</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1078</v>
+        <v>-1.3182</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9129</v>
+        <v>-0.3479</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.643</v>
+        <v>-0.5109</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7301</v>
+        <v>0.163</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. JEKIRI</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.743</v>
+        <v>-2.808</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4885</v>
+        <v>-0.1546</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2544</v>
+        <v>-2.6534</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.3933</v>
+        <v>-3.0614</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.8007</v>
+        <v>-1.1475</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5925</v>
+        <v>-1.9139</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.9058</v>
+        <v>0.2983</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.0531</v>
+        <v>0.1043</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1472</v>
+        <v>0.1939</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4874</v>
+        <v>-3.3596</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7477</v>
+        <v>-1.2518</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7398</v>
+        <v>-2.1078</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6503</v>
+        <v>-0.9966</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5771</v>
+        <v>-1.525</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0732</v>
+        <v>0.5285</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. LAKIC</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.0474</v>
+        <v>-3.3676</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7188</v>
+        <v>-2.496</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3286</v>
+        <v>-0.8716</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.92</v>
+        <v>-3.8425</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6386</v>
+        <v>-0.761</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2814</v>
+        <v>-3.0816</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8973</v>
+        <v>-1.3443</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9341</v>
+        <v>0.1547</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0368</v>
+        <v>-1.4991</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0227</v>
+        <v>-2.4982</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7045</v>
+        <v>-0.9157</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3182</v>
+        <v>-1.5825</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5913</v>
+        <v>-0.8472</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8215</v>
+        <v>-1.1516</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2302</v>
+        <v>0.3044</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.4624</v>
+        <v>-3.3877</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.122</v>
+        <v>-3.0473</v>
       </c>
       <c r="F7" t="n">
         <v>-0.3404</v>
@@ -1000,10 +1000,10 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9041</v>
+        <v>-0.8294</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3339</v>
+        <v>-0.2592</v>
       </c>
       <c r="U7" t="n">
         <v>-0.5702</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.8216</v>
+        <v>-4.2136</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6139</v>
+        <v>-0.6698</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2077</v>
+        <v>-3.5438</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8425</v>
+        <v>-1.8104</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.761</v>
+        <v>-0.7765</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.0816</v>
+        <v>-1.0339</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3443</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1547</v>
+        <v>0.6218</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4991</v>
+        <v>-0.5556</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4982</v>
+        <v>-1.8766</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9157</v>
+        <v>-1.3983</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5825</v>
+        <v>-0.4783</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3012</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2696</v>
+        <v>-0.6484</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0316</v>
+        <v>-0.0769</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3943</v>
+        <v>-1.214</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3943</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.8871</v>
+        <v>-4.9554</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1416</v>
+        <v>-3.594</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.7455</v>
+        <v>-1.3614</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8104</v>
+        <v>-4.9584</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7765</v>
+        <v>-0.6421</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0339</v>
+        <v>-4.3164</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06619999999999999</v>
+        <v>-2.9141</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6218</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5556</v>
+        <v>-2.9982</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8766</v>
+        <v>-2.0443</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3983</v>
+        <v>-0.7261</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4783</v>
+        <v>-1.3182</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3987</v>
+        <v>-0.9247</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1202</v>
+        <v>-0.6798</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2785</v>
+        <v>-0.2449</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>T. JEKIRI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.7206</v>
+        <v>-5.0089</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2584</v>
+        <v>-3.1831</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4622</v>
+        <v>-1.8258</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.9584</v>
+        <v>-4.3933</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6421</v>
+        <v>-2.8007</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.3164</v>
+        <v>-1.5925</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.9141</v>
+        <v>-1.9058</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08400000000000001</v>
+        <v>-2.0531</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.9982</v>
+        <v>0.1472</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0443</v>
+        <v>-2.4874</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7261</v>
+        <v>-0.7477</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3182</v>
+        <v>-1.7398</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.69</v>
+        <v>0.3844</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3443</v>
+        <v>-0.1175</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3457</v>
+        <v>0.5019</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.9223</v>
+        <v>-10.6117</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.773300000000001</v>
+        <v>-8.4627</v>
       </c>
       <c r="F11" t="n">
         <v>-2.149</v>
@@ -1312,10 +1312,10 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9946</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.643</v>
+        <v>-1.3324</v>
       </c>
       <c r="U11" t="n">
         <v>0.6484</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-37.4646</v>
+        <v>-37.0912</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.9353</v>
+        <v>-19.562</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.5292</v>
+        <v>-17.5293</v>
       </c>
       <c r="G12" t="n">
         <v>-32.1476</v>
@@ -1390,13 +1390,13 @@
         <v>9.2783</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.626299999999999</v>
+        <v>-7.2528</v>
       </c>
       <c r="T12" t="n">
-        <v>-8.351200000000002</v>
+        <v>-7.977599999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7248999999999999</v>
+        <v>0.7249</v>
       </c>
       <c r="V12" t="n">
         <v>3.4691</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.6314</v>
+        <v>13.1596</v>
       </c>
       <c r="E13" t="n">
-        <v>8.5405</v>
+        <v>8.0687</v>
       </c>
       <c r="F13" t="n">
         <v>5.0909</v>
@@ -1468,10 +1468,10 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1464</v>
+        <v>1.6746</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9911</v>
+        <v>0.5192</v>
       </c>
       <c r="U13" t="n">
         <v>1.1554</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.957599999999999</v>
+        <v>10.1694</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0745</v>
+        <v>6.7822</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8831</v>
+        <v>3.3872</v>
       </c>
       <c r="G14" t="n">
         <v>8.3688</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1946</v>
+        <v>1.0172</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7468</v>
+        <v>-0.0391</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5522</v>
+        <v>1.0563</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0722</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.723699999999999</v>
+        <v>7.5778</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7995</v>
+        <v>3.6199</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9242</v>
+        <v>3.9578</v>
       </c>
       <c r="G15" t="n">
         <v>4.0672</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6564</v>
+        <v>1.5105</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6948</v>
+        <v>0.5153</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9616</v>
+        <v>0.9952</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2604</v>
+        <v>4.5369</v>
       </c>
       <c r="E16" t="n">
-        <v>4.452</v>
+        <v>4.0982</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8084</v>
+        <v>0.4387</v>
       </c>
       <c r="G16" t="n">
         <v>4.1155</v>
@@ -1702,13 +1702,13 @@
         <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0548</v>
+        <v>0.3312</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0351</v>
+        <v>-0.389</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0899</v>
+        <v>0.7202</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1418</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8862</v>
+        <v>3.5007</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9966</v>
+        <v>3.3505</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8895</v>
+        <v>0.1502</v>
       </c>
       <c r="G17" t="n">
         <v>4.1976</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0675</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7389</v>
+        <v>-0.3851</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8064</v>
+        <v>1.0671</v>
       </c>
       <c r="V17" t="n">
         <v>-2.5387</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7531</v>
+        <v>1.5166</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8161</v>
+        <v>0.3443</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9370000000000001</v>
+        <v>1.1722</v>
       </c>
       <c r="G18" t="n">
         <v>2.4336</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2473</v>
+        <v>0.0108</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4288</v>
+        <v>-0.0431</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1814</v>
+        <v>0.0538</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5174</v>
+        <v>0.8205</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4299</v>
+        <v>-1.194</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9473</v>
+        <v>2.0145</v>
       </c>
       <c r="G19" t="n">
         <v>1.7926</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.203</v>
+        <v>0.1002</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2829</v>
+        <v>-0.047</v>
       </c>
       <c r="U19" t="n">
-        <v>0.08</v>
+        <v>0.1472</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2036</v>
+        <v>0.4527</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4514</v>
+        <v>-0.0975</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2478</v>
+        <v>0.5502</v>
       </c>
       <c r="G20" t="n">
         <v>1.347</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4784</v>
+        <v>0.1779</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7389</v>
+        <v>-0.3851</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2605</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6802</v>
+        <v>-0.3942</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1703</v>
+        <v>-0.0523</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5099</v>
+        <v>-0.3419</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4188</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2614</v>
+        <v>0.0246</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U21" t="n">
-        <v>0.112</v>
+        <v>0.2801</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0392</v>
+        <v>-1.14</v>
       </c>
       <c r="E22" t="n">
         <v>-3.1086</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0694</v>
+        <v>1.9686</v>
       </c>
       <c r="G22" t="n">
         <v>1.0797</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3087</v>
+        <v>1.2079</v>
       </c>
       <c r="T22" t="n">
         <v>0.0395</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2691</v>
+        <v>1.1683</v>
       </c>
       <c r="V22" t="n">
         <v>0.2836</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3421</v>
+        <v>-2.7352</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5259</v>
+        <v>-4.8182</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1838</v>
+        <v>2.083</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3204</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2825</v>
+        <v>0.8894</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.963</v>
+        <v>-0.2552</v>
       </c>
       <c r="U23" t="n">
-        <v>1.2454</v>
+        <v>1.1446</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>37.46469999999999</v>
+        <v>37.4648</v>
       </c>
       <c r="E24" t="n">
-        <v>16.9931</v>
+        <v>16.9932</v>
       </c>
       <c r="F24" t="n">
-        <v>20.4715</v>
+        <v>20.4714</v>
       </c>
       <c r="G24" t="n">
         <v>32.1478</v>
@@ -2326,13 +2326,13 @@
         <v>10.438</v>
       </c>
       <c r="S24" t="n">
-        <v>7.6262</v>
+        <v>7.626300000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7247999999999999</v>
+        <v>-0.7251000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>8.351100000000001</v>
+        <v>8.3512</v>
       </c>
       <c r="V24" t="n">
         <v>-3.4691</v>
